--- a/dataEDT-ELT-S1-2027.xlsx
+++ b/dataEDT-ELT-S1-2027.xlsx
@@ -22303,7 +22303,7 @@
         <v>1636</v>
       </c>
       <c r="F632" t="s">
-        <v>1691</v>
+        <v>1652</v>
       </c>
       <c r="G632" t="s">
         <v>1806</v>
@@ -29973,7 +29973,7 @@
         <v>1637</v>
       </c>
       <c r="F927" t="s">
-        <v>1687</v>
+        <v>1652</v>
       </c>
       <c r="G927" t="s">
         <v>1818</v>
@@ -31013,7 +31013,7 @@
         <v>1637</v>
       </c>
       <c r="F967" t="s">
-        <v>1687</v>
+        <v>1652</v>
       </c>
       <c r="G967" t="s">
         <v>1820</v>
